--- a/data/Transitions.xlsx
+++ b/data/Transitions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\mohammad\projects\Thesis\hemophilia\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A341FD60-8836-45DF-A866-6AC59188AD00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{217266E8-0382-43D0-BC83-844C536B2657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7944" yWindow="36" windowWidth="15276" windowHeight="12204" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="on_demand" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="27">
   <si>
     <t>Healthy</t>
   </si>
@@ -112,6 +112,12 @@
   </si>
   <si>
     <t>ALTBR (10Y)</t>
+  </si>
+  <si>
+    <t>Joint_Bleeding</t>
+  </si>
+  <si>
+    <t>Bleeding</t>
   </si>
 </sst>
 </file>
@@ -120,8 +126,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="168" formatCode="0.000"/>
-    <numFmt numFmtId="173" formatCode="0.000000%"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.000000%"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -212,13 +218,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -505,7 +511,7 @@
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.109375" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
     <col min="2" max="6" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -517,10 +523,10 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -562,7 +568,7 @@
     </row>
     <row r="3" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="B3" s="11">
         <f>1-SUM(C3:F3)</f>
@@ -590,7 +596,7 @@
     </row>
     <row r="4" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="B4" s="11">
         <f>1-SUM(C4:F4)</f>
